--- a/tudo modelado.xlsx
+++ b/tudo modelado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juan\Desktop\Task manager\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FF63684-E3D7-4340-AF51-E68DB5BAC7A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1CEA4C-AAE4-49C8-9961-B88C8190371A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="27870" windowHeight="15030" firstSheet="2" activeTab="2" xr2:uid="{C6185A76-6520-46ED-8A33-B9C8D95F8CD0}"/>
+    <workbookView xWindow="3225" yWindow="1770" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{C6185A76-6520-46ED-8A33-B9C8D95F8CD0}"/>
   </bookViews>
   <sheets>
     <sheet name="Ciclo" sheetId="1" r:id="rId1"/>
@@ -399,13 +399,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1188,7 +1187,7 @@
       <c r="E2" s="4">
         <v>45835</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" t="s">
         <v>50</v>
       </c>
       <c r="G2" s="3">
@@ -1197,10 +1196,10 @@
       <c r="H2">
         <v>2.581</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="5" t="s">
+      <c r="I2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J2" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1220,7 +1219,7 @@
       <c r="E3" s="4">
         <v>45835</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" t="s">
         <v>38</v>
       </c>
       <c r="G3" s="3">
@@ -1229,10 +1228,10 @@
       <c r="H3">
         <v>3.7410000000000001</v>
       </c>
-      <c r="I3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1252,7 +1251,7 @@
       <c r="E4" s="4">
         <v>45835</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" t="s">
         <v>41</v>
       </c>
       <c r="G4" s="3">
@@ -1261,10 +1260,10 @@
       <c r="H4">
         <v>4.9320000000000004</v>
       </c>
-      <c r="I4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" t="s">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1284,7 +1283,7 @@
       <c r="E5" s="4">
         <v>45839</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
       <c r="G5" s="3">
@@ -1293,10 +1292,10 @@
       <c r="H5">
         <v>1.8839999999999999</v>
       </c>
-      <c r="I5" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J5" s="5" t="s">
+      <c r="I5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1316,7 +1315,7 @@
       <c r="E6" s="4">
         <v>45839</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" t="s">
         <v>39</v>
       </c>
       <c r="G6" s="3">
@@ -1325,10 +1324,10 @@
       <c r="H6">
         <v>3.41</v>
       </c>
-      <c r="I6" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="5" t="s">
+      <c r="I6" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1348,7 +1347,7 @@
       <c r="E7" s="4">
         <v>45839</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" t="s">
         <v>50</v>
       </c>
       <c r="G7" s="3">
@@ -1357,10 +1356,10 @@
       <c r="H7">
         <v>2.0013999999999998</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" t="s">
         <v>54</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1380,7 +1379,7 @@
       <c r="E8" s="4">
         <v>45840</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" t="s">
         <v>52</v>
       </c>
       <c r="G8" s="3">
@@ -1389,10 +1388,10 @@
       <c r="H8">
         <v>1.3406</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" t="s">
         <v>59</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1412,7 +1411,7 @@
       <c r="E9" s="4">
         <v>45841</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" t="s">
         <v>40</v>
       </c>
       <c r="G9" s="3">
@@ -1421,10 +1420,10 @@
       <c r="H9">
         <v>3.6480000000000001</v>
       </c>
-      <c r="I9" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1444,7 +1443,7 @@
       <c r="E10" s="4">
         <v>45845</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" t="s">
         <v>40</v>
       </c>
       <c r="G10" s="3">
@@ -1453,10 +1452,10 @@
       <c r="H10">
         <v>2.6980599999999999</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" t="s">
         <v>61</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1476,7 +1475,7 @@
       <c r="E11" s="4">
         <v>45855</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="3">
@@ -1485,10 +1484,10 @@
       <c r="H11">
         <v>3.02</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" t="s">
         <v>58</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1508,7 +1507,7 @@
       <c r="E12" s="4">
         <v>45859</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" t="s">
         <v>39</v>
       </c>
       <c r="G12" s="3">
@@ -1517,10 +1516,10 @@
       <c r="H12">
         <v>2.2240000000000002</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" t="s">
         <v>63</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1540,7 +1539,7 @@
       <c r="E13" s="4">
         <v>45860</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="3">
@@ -1549,10 +1548,10 @@
       <c r="H13">
         <v>1.028</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" t="s">
         <v>57</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1572,7 +1571,7 @@
       <c r="E14" s="4">
         <v>45860</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" t="s">
         <v>50</v>
       </c>
       <c r="G14" s="3">
@@ -1581,10 +1580,10 @@
       <c r="H14">
         <v>0</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" t="s">
         <v>60</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1604,7 +1603,7 @@
       <c r="E15" s="4">
         <v>45861</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" t="s">
         <v>38</v>
       </c>
       <c r="G15" s="3">
@@ -1613,10 +1612,10 @@
       <c r="H15">
         <v>2.8864000000000001</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" t="s">
         <v>55</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1636,7 +1635,7 @@
       <c r="E16" s="4">
         <v>45862</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" t="s">
         <v>38</v>
       </c>
       <c r="G16" s="3">
@@ -1645,10 +1644,10 @@
       <c r="H16">
         <v>1.6292</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1668,7 +1667,7 @@
       <c r="E17" s="4">
         <v>45863</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" t="s">
         <v>40</v>
       </c>
       <c r="G17" s="3">
@@ -1677,10 +1676,10 @@
       <c r="H17">
         <v>2.0884</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" t="s">
         <v>62</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1700,7 +1699,7 @@
       <c r="E18" s="4">
         <v>45867</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" t="s">
         <v>31</v>
       </c>
       <c r="G18" s="3">
@@ -1709,10 +1708,10 @@
       <c r="H18">
         <v>0</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" t="s">
         <v>65</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1732,7 +1731,7 @@
       <c r="E19" s="4">
         <v>45872</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" t="s">
         <v>39</v>
       </c>
       <c r="G19" s="3">
@@ -1741,10 +1740,10 @@
       <c r="H19">
         <v>0.95250000000000001</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" t="s">
         <v>64</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1764,7 +1763,7 @@
       <c r="E20" s="4">
         <v>45873</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" t="s">
         <v>40</v>
       </c>
       <c r="G20" s="3">
@@ -1773,10 +1772,10 @@
       <c r="H20">
         <v>1.0445</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" t="s">
         <v>68</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1796,7 +1795,7 @@
       <c r="E21" s="4">
         <v>45874</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" t="s">
         <v>38</v>
       </c>
       <c r="G21" s="3">
@@ -1805,10 +1804,10 @@
       <c r="H21">
         <v>0.52305999999999997</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" t="s">
         <v>67</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1828,7 +1827,7 @@
       <c r="E22" s="4">
         <v>45874</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" t="s">
         <v>41</v>
       </c>
       <c r="G22" s="3">
@@ -1837,10 +1836,10 @@
       <c r="H22">
         <v>4.0339</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" t="s">
         <v>56</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1860,7 +1859,7 @@
       <c r="E23" s="4">
         <v>45875</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" t="s">
         <v>40</v>
       </c>
       <c r="G23" s="3">
@@ -1869,10 +1868,10 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" t="s">
         <v>70</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1892,7 +1891,7 @@
       <c r="E24" s="4">
         <v>45875</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" t="s">
         <v>39</v>
       </c>
       <c r="G24" s="3">
@@ -1901,10 +1900,10 @@
       <c r="H24">
         <v>0</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" t="s">
         <v>69</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1924,7 +1923,7 @@
       <c r="E25" s="4">
         <v>45876</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" t="s">
         <v>38</v>
       </c>
       <c r="G25" s="3">
@@ -1933,10 +1932,10 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" t="s">
         <v>71</v>
       </c>
-      <c r="J25" s="5" t="s">
+      <c r="J25" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1956,7 +1955,7 @@
       <c r="E26" s="4">
         <v>45876</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" t="s">
         <v>41</v>
       </c>
       <c r="G26" s="3">
@@ -1965,10 +1964,10 @@
       <c r="H26">
         <v>2.9708999999999999</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" t="s">
         <v>72</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" t="s">
         <v>51</v>
       </c>
     </row>
@@ -1988,7 +1987,7 @@
       <c r="E27" s="4">
         <v>45877</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" t="s">
         <v>41</v>
       </c>
       <c r="G27" s="3">
@@ -1997,10 +1996,10 @@
       <c r="H27">
         <v>2.1595</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" t="s">
         <v>73</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2020,7 +2019,7 @@
       <c r="E28" s="4">
         <v>45878</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" t="s">
         <v>41</v>
       </c>
       <c r="G28" s="3">
@@ -2029,10 +2028,10 @@
       <c r="H28">
         <v>0</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" t="s">
         <v>74</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2052,7 +2051,7 @@
       <c r="E29" s="4">
         <v>45882</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" t="s">
         <v>9</v>
       </c>
       <c r="G29" s="3">
@@ -2061,10 +2060,10 @@
       <c r="H29">
         <v>0.23730000000000001</v>
       </c>
-      <c r="I29" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J29" s="5" t="s">
+      <c r="I29" t="s">
+        <v>51</v>
+      </c>
+      <c r="J29" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2084,7 +2083,7 @@
       <c r="E30" s="4">
         <v>45883</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="F30" t="s">
         <v>7</v>
       </c>
       <c r="G30" s="3">
@@ -2093,10 +2092,10 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J30" s="5" t="s">
+      <c r="I30" t="s">
+        <v>51</v>
+      </c>
+      <c r="J30" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2116,7 +2115,7 @@
       <c r="E31" s="4">
         <v>45884</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="F31" t="s">
         <v>9</v>
       </c>
       <c r="G31" s="3">
@@ -2125,10 +2124,10 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" s="5" t="s">
+      <c r="I31" t="s">
         <v>76</v>
       </c>
-      <c r="J31" s="5" t="s">
+      <c r="J31" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2148,7 +2147,7 @@
       <c r="E32" s="4">
         <v>45887</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="F32" t="s">
         <v>8</v>
       </c>
       <c r="G32" s="3">
@@ -2157,10 +2156,10 @@
       <c r="H32">
         <v>0.81950000000000001</v>
       </c>
-      <c r="I32" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="5" t="s">
+      <c r="I32" t="s">
+        <v>51</v>
+      </c>
+      <c r="J32" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2180,7 +2179,7 @@
       <c r="E33" s="4">
         <v>45888</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="F33" t="s">
         <v>8</v>
       </c>
       <c r="G33" s="3">
@@ -2189,10 +2188,10 @@
       <c r="H33">
         <v>0</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I33" t="s">
         <v>77</v>
       </c>
-      <c r="J33" s="5" t="s">
+      <c r="J33" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2212,7 +2211,7 @@
       <c r="E34" s="4">
         <v>45888</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="3">
@@ -2221,10 +2220,10 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J34" s="5" t="s">
+      <c r="I34" t="s">
+        <v>51</v>
+      </c>
+      <c r="J34" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2244,7 +2243,7 @@
       <c r="E35" s="4">
         <v>45889</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="F35" t="s">
         <v>11</v>
       </c>
       <c r="G35" s="3">
@@ -2253,10 +2252,10 @@
       <c r="H35">
         <v>0</v>
       </c>
-      <c r="I35" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J35" s="5" t="s">
+      <c r="I35" t="s">
+        <v>51</v>
+      </c>
+      <c r="J35" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2276,7 +2275,7 @@
       <c r="E36" s="4">
         <v>45889</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" t="s">
         <v>18</v>
       </c>
       <c r="G36" s="3">
@@ -2285,10 +2284,10 @@
       <c r="H36">
         <v>0</v>
       </c>
-      <c r="I36" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" s="5" t="s">
+      <c r="I36" t="s">
+        <v>51</v>
+      </c>
+      <c r="J36" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2308,7 +2307,7 @@
       <c r="E37" s="4">
         <v>45890</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" t="s">
         <v>12</v>
       </c>
       <c r="G37" s="3">
@@ -2317,10 +2316,10 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J37" s="5" t="s">
+      <c r="I37" t="s">
+        <v>51</v>
+      </c>
+      <c r="J37" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2340,7 +2339,7 @@
       <c r="E38" s="4">
         <v>45890</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" t="s">
         <v>13</v>
       </c>
       <c r="G38" s="3">
@@ -2349,10 +2348,10 @@
       <c r="H38">
         <v>0</v>
       </c>
-      <c r="I38" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J38" s="5" t="s">
+      <c r="I38" t="s">
+        <v>51</v>
+      </c>
+      <c r="J38" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2372,7 +2371,7 @@
       <c r="E39" s="4">
         <v>45891</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="F39" t="s">
         <v>14</v>
       </c>
       <c r="G39" s="3">
@@ -2381,10 +2380,10 @@
       <c r="H39">
         <v>0</v>
       </c>
-      <c r="I39" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J39" s="5" t="s">
+      <c r="I39" t="s">
+        <v>51</v>
+      </c>
+      <c r="J39" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2404,7 +2403,7 @@
       <c r="E40" s="4">
         <v>45892</v>
       </c>
-      <c r="F40" s="5" t="s">
+      <c r="F40" t="s">
         <v>16</v>
       </c>
       <c r="G40" s="3">
@@ -2413,10 +2412,10 @@
       <c r="H40">
         <v>0</v>
       </c>
-      <c r="I40" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J40" s="5" t="s">
+      <c r="I40" t="s">
+        <v>51</v>
+      </c>
+      <c r="J40" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2436,7 +2435,7 @@
       <c r="E41" s="4">
         <v>45892</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="F41" t="s">
         <v>17</v>
       </c>
       <c r="G41" s="3">
@@ -2445,10 +2444,10 @@
       <c r="H41">
         <v>0</v>
       </c>
-      <c r="I41" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J41" s="5" t="s">
+      <c r="I41" t="s">
+        <v>51</v>
+      </c>
+      <c r="J41" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2468,7 +2467,7 @@
       <c r="E42" s="4">
         <v>45892</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" t="s">
         <v>15</v>
       </c>
       <c r="G42" s="3">
@@ -2477,10 +2476,10 @@
       <c r="H42">
         <v>0</v>
       </c>
-      <c r="I42" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J42" s="5" t="s">
+      <c r="I42" t="s">
+        <v>51</v>
+      </c>
+      <c r="J42" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2500,7 +2499,7 @@
       <c r="E43" s="4">
         <v>45883</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" t="s">
         <v>7</v>
       </c>
       <c r="G43" s="3">
@@ -2509,10 +2508,10 @@
       <c r="H43">
         <v>1.1425000000000001</v>
       </c>
-      <c r="I43" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J43" s="5" t="s">
+      <c r="I43" t="s">
+        <v>51</v>
+      </c>
+      <c r="J43" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2532,7 +2531,7 @@
       <c r="E44" s="4">
         <v>45884</v>
       </c>
-      <c r="F44" s="5" t="s">
+      <c r="F44" t="s">
         <v>9</v>
       </c>
       <c r="G44" s="3">
@@ -2541,10 +2540,10 @@
       <c r="H44">
         <v>0</v>
       </c>
-      <c r="I44" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J44" s="5" t="s">
+      <c r="I44" t="s">
+        <v>51</v>
+      </c>
+      <c r="J44" t="s">
         <v>79</v>
       </c>
     </row>
@@ -2564,7 +2563,7 @@
       <c r="E45" s="4">
         <v>45888</v>
       </c>
-      <c r="F45" s="5" t="s">
+      <c r="F45" t="s">
         <v>8</v>
       </c>
       <c r="G45" s="3">
@@ -2573,10 +2572,10 @@
       <c r="H45">
         <v>1.45</v>
       </c>
-      <c r="I45" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J45" s="5" t="s">
+      <c r="I45" t="s">
+        <v>51</v>
+      </c>
+      <c r="J45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -2596,7 +2595,7 @@
       <c r="E46" s="4">
         <v>45888</v>
       </c>
-      <c r="F46" s="5" t="s">
+      <c r="F46" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="3">
@@ -2605,10 +2604,10 @@
       <c r="H46">
         <v>0.97140000000000004</v>
       </c>
-      <c r="I46" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J46" s="5" t="s">
+      <c r="I46" t="s">
+        <v>51</v>
+      </c>
+      <c r="J46" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2628,7 +2627,7 @@
       <c r="E47" s="4">
         <v>45889</v>
       </c>
-      <c r="F47" s="5" t="s">
+      <c r="F47" t="s">
         <v>11</v>
       </c>
       <c r="G47" s="3">
@@ -2637,10 +2636,10 @@
       <c r="H47">
         <v>0.67800000000000005</v>
       </c>
-      <c r="I47" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J47" s="5" t="s">
+      <c r="I47" t="s">
+        <v>51</v>
+      </c>
+      <c r="J47" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2660,7 +2659,7 @@
       <c r="E48" s="4">
         <v>45889</v>
       </c>
-      <c r="F48" s="5" t="s">
+      <c r="F48" t="s">
         <v>18</v>
       </c>
       <c r="G48" s="3">
@@ -2669,10 +2668,10 @@
       <c r="H48">
         <v>0.36730000000000002</v>
       </c>
-      <c r="I48" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J48" s="5" t="s">
+      <c r="I48" t="s">
+        <v>51</v>
+      </c>
+      <c r="J48" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2692,7 +2691,7 @@
       <c r="E49" s="4">
         <v>45890</v>
       </c>
-      <c r="F49" s="5" t="s">
+      <c r="F49" t="s">
         <v>12</v>
       </c>
       <c r="G49" s="3">
@@ -2701,10 +2700,10 @@
       <c r="H49">
         <v>0.67600000000000005</v>
       </c>
-      <c r="I49" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J49" s="5" t="s">
+      <c r="I49" t="s">
+        <v>51</v>
+      </c>
+      <c r="J49" t="s">
         <v>84</v>
       </c>
     </row>
@@ -2724,7 +2723,7 @@
       <c r="E50" s="4">
         <v>45890</v>
       </c>
-      <c r="F50" s="5" t="s">
+      <c r="F50" t="s">
         <v>13</v>
       </c>
       <c r="G50" s="3">
@@ -2733,10 +2732,10 @@
       <c r="H50">
         <v>0.59250000000000003</v>
       </c>
-      <c r="I50" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J50" s="5" t="s">
+      <c r="I50" t="s">
+        <v>51</v>
+      </c>
+      <c r="J50" t="s">
         <v>85</v>
       </c>
     </row>
@@ -2756,7 +2755,7 @@
       <c r="E51" s="4">
         <v>45891</v>
       </c>
-      <c r="F51" s="5" t="s">
+      <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" s="3">
@@ -2765,10 +2764,10 @@
       <c r="H51">
         <v>0.58169999999999999</v>
       </c>
-      <c r="I51" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J51" s="5" t="s">
+      <c r="I51" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" t="s">
         <v>86</v>
       </c>
     </row>
@@ -2788,7 +2787,7 @@
       <c r="E52" s="4">
         <v>45892</v>
       </c>
-      <c r="F52" s="5" t="s">
+      <c r="F52" t="s">
         <v>16</v>
       </c>
       <c r="G52" s="3">
@@ -2797,10 +2796,10 @@
       <c r="H52">
         <v>0.48309999999999997</v>
       </c>
-      <c r="I52" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J52" s="5" t="s">
+      <c r="I52" t="s">
+        <v>51</v>
+      </c>
+      <c r="J52" t="s">
         <v>87</v>
       </c>
     </row>
@@ -2820,7 +2819,7 @@
       <c r="E53" s="4">
         <v>45892</v>
       </c>
-      <c r="F53" s="5" t="s">
+      <c r="F53" t="s">
         <v>15</v>
       </c>
       <c r="G53" s="3">
@@ -2829,10 +2828,10 @@
       <c r="H53">
         <v>0.36870000000000003</v>
       </c>
-      <c r="I53" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J53" s="5" t="s">
+      <c r="I53" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2852,7 +2851,7 @@
       <c r="E54" s="4">
         <v>45897</v>
       </c>
-      <c r="F54" s="5" t="s">
+      <c r="F54" t="s">
         <v>7</v>
       </c>
       <c r="G54" s="3">
@@ -2861,10 +2860,10 @@
       <c r="H54">
         <v>0</v>
       </c>
-      <c r="I54" s="5" t="s">
+      <c r="I54" t="s">
         <v>89</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2884,7 +2883,7 @@
       <c r="E55" s="4">
         <v>45898</v>
       </c>
-      <c r="F55" s="5" t="s">
+      <c r="F55" t="s">
         <v>8</v>
       </c>
       <c r="G55" s="3">
@@ -2893,10 +2892,10 @@
       <c r="H55">
         <v>0.57920000000000005</v>
       </c>
-      <c r="I55" s="5" t="s">
+      <c r="I55" t="s">
         <v>90</v>
       </c>
-      <c r="J55" s="5" t="s">
+      <c r="J55" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2916,7 +2915,7 @@
       <c r="E56" s="4">
         <v>45900</v>
       </c>
-      <c r="F56" s="5" t="s">
+      <c r="F56" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="3">
@@ -2925,10 +2924,10 @@
       <c r="H56">
         <v>0.27100000000000002</v>
       </c>
-      <c r="I56" s="5" t="s">
+      <c r="I56" t="s">
         <v>91</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2948,7 +2947,7 @@
       <c r="E57" s="4">
         <v>45904</v>
       </c>
-      <c r="F57" s="5" t="s">
+      <c r="F57" t="s">
         <v>8</v>
       </c>
       <c r="G57" s="3">
@@ -2957,10 +2956,10 @@
       <c r="H57">
         <v>0</v>
       </c>
-      <c r="I57" s="5" t="s">
+      <c r="I57" t="s">
         <v>92</v>
       </c>
-      <c r="J57" s="5" t="s">
+      <c r="J57" t="s">
         <v>51</v>
       </c>
     </row>
@@ -2980,7 +2979,7 @@
       <c r="E58" s="4">
         <v>45904</v>
       </c>
-      <c r="F58" s="5" t="s">
+      <c r="F58" t="s">
         <v>11</v>
       </c>
       <c r="G58" s="3">
@@ -2989,10 +2988,10 @@
       <c r="H58">
         <v>0</v>
       </c>
-      <c r="I58" s="5" t="s">
+      <c r="I58" t="s">
         <v>93</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3012,7 +3011,7 @@
       <c r="E59" s="4">
         <v>45912</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="F59" t="s">
         <v>12</v>
       </c>
       <c r="G59" s="3">
@@ -3021,10 +3020,10 @@
       <c r="H59">
         <v>0</v>
       </c>
-      <c r="I59" s="5" t="s">
+      <c r="I59" t="s">
         <v>94</v>
       </c>
-      <c r="J59" s="5" t="s">
+      <c r="J59" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3044,7 +3043,7 @@
       <c r="E60" s="4">
         <v>45926</v>
       </c>
-      <c r="F60" s="5" t="s">
+      <c r="F60" t="s">
         <v>15</v>
       </c>
       <c r="G60" s="3">
@@ -3053,10 +3052,10 @@
       <c r="H60">
         <v>0</v>
       </c>
-      <c r="I60" s="5" t="s">
+      <c r="I60" t="s">
         <v>95</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="J60" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3076,7 +3075,7 @@
       <c r="E61" s="4">
         <v>45926</v>
       </c>
-      <c r="F61" s="5" t="s">
+      <c r="F61" t="s">
         <v>16</v>
       </c>
       <c r="G61" s="3">
@@ -3085,10 +3084,10 @@
       <c r="H61">
         <v>0</v>
       </c>
-      <c r="I61" s="5" t="s">
+      <c r="I61" t="s">
         <v>96</v>
       </c>
-      <c r="J61" s="5" t="s">
+      <c r="J61" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3108,7 +3107,7 @@
       <c r="E62" s="4">
         <v>45926</v>
       </c>
-      <c r="F62" s="5" t="s">
+      <c r="F62" t="s">
         <v>17</v>
       </c>
       <c r="G62" s="3">
@@ -3117,10 +3116,10 @@
       <c r="H62">
         <v>0</v>
       </c>
-      <c r="I62" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J62" s="5" t="s">
+      <c r="I62" t="s">
+        <v>51</v>
+      </c>
+      <c r="J62" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3140,7 +3139,7 @@
       <c r="E63" s="4">
         <v>45949</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F63" t="s">
         <v>13</v>
       </c>
       <c r="G63" s="3">
@@ -3149,10 +3148,10 @@
       <c r="H63">
         <v>0</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I63" t="s">
         <v>97</v>
       </c>
-      <c r="J63" s="5" t="s">
+      <c r="J63" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3172,7 +3171,7 @@
       <c r="E64" s="4">
         <v>45949</v>
       </c>
-      <c r="F64" s="5" t="s">
+      <c r="F64" t="s">
         <v>14</v>
       </c>
       <c r="G64" s="3">
@@ -3181,10 +3180,10 @@
       <c r="H64">
         <v>0</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="I64" t="s">
         <v>98</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3204,7 +3203,7 @@
       <c r="E65" s="4">
         <v>45949</v>
       </c>
-      <c r="F65" s="5" t="s">
+      <c r="F65" t="s">
         <v>18</v>
       </c>
       <c r="G65" s="3">
@@ -3213,10 +3212,10 @@
       <c r="H65">
         <v>0</v>
       </c>
-      <c r="I65" s="5" t="s">
+      <c r="I65" t="s">
         <v>99</v>
       </c>
-      <c r="J65" s="5" t="s">
+      <c r="J65" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3236,7 +3235,7 @@
       <c r="E66" s="4">
         <v>45949</v>
       </c>
-      <c r="F66" s="5" t="s">
+      <c r="F66" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="3">
@@ -3245,10 +3244,10 @@
       <c r="H66">
         <v>0</v>
       </c>
-      <c r="I66" s="5" t="s">
+      <c r="I66" t="s">
         <v>100</v>
       </c>
-      <c r="J66" s="5" t="s">
+      <c r="J66" t="s">
         <v>51</v>
       </c>
     </row>
